--- a/tests/TC-18/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-18/results/timetable_all_departments_even.xlsx
@@ -178,15 +178,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -831,7 +831,108 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>MA163
 TUT
@@ -839,46 +940,30 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="9" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -886,111 +971,26 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="9" t="inlineStr"/>
-      <c r="R3" s="9" t="inlineStr"/>
-      <c r="S3" s="9" t="inlineStr"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr"/>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr"/>
-      <c r="Q4" s="9" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="9" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="9" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: C004
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
-      <c r="Q5" s="9" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1008,28 +1008,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1104,9 +1104,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D3:G3"/>
+  <mergeCells count="3">
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="F2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1263,7 +1264,108 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="8" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="11" t="n"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="8" t="inlineStr"/>
+      <c r="R2" s="8" t="inlineStr"/>
+      <c r="S2" s="8" t="inlineStr"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="9" t="inlineStr">
         <is>
           <t>MA163
 TUT
@@ -1271,46 +1373,30 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="9" t="inlineStr"/>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="11" t="n"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>MA163
 LEC
@@ -1318,111 +1404,26 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="E3" s="11" t="n"/>
-      <c r="F3" s="11" t="n"/>
-      <c r="G3" s="12" t="n"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="E5" s="10" t="n"/>
+      <c r="F5" s="10" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
+      <c r="K5" s="8" t="inlineStr"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="9" t="inlineStr"/>
-      <c r="R3" s="9" t="inlineStr"/>
-      <c r="S3" s="9" t="inlineStr"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr"/>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr"/>
-      <c r="Q4" s="9" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="9" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr"/>
-      <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="9" t="inlineStr"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: C004
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N5" s="12" t="n"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
-      <c r="Q5" s="9" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1440,28 +1441,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="9" t="inlineStr"/>
-      <c r="N6" s="9" t="inlineStr"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1536,9 +1537,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D3:G3"/>
+  <mergeCells count="3">
+    <mergeCell ref="D5:G5"/>
+    <mergeCell ref="O4:Q4"/>
+    <mergeCell ref="F2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1695,28 +1697,145 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>MA163
 TUT
@@ -1724,130 +1843,20 @@
 Dr. Anand</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr"/>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="9" t="inlineStr"/>
-      <c r="R3" s="9" t="inlineStr"/>
-      <c r="S3" s="9" t="inlineStr"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr"/>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr"/>
-      <c r="Q4" s="9" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="9" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: C004
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr"/>
-      <c r="N5" s="9" t="inlineStr"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
-      <c r="Q5" s="9" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1865,35 +1874,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: C004
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -1968,9 +1970,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="G5:J5"/>
+  <mergeCells count="3">
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2127,159 +2130,166 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr"/>
-      <c r="D2" s="9" t="inlineStr"/>
-      <c r="E2" s="9" t="inlineStr"/>
-      <c r="F2" s="9" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr"/>
-      <c r="H2" s="9" t="inlineStr"/>
-      <c r="I2" s="9" t="inlineStr"/>
-      <c r="J2" s="9" t="inlineStr"/>
-      <c r="K2" s="9" t="inlineStr"/>
-      <c r="L2" s="10" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr"/>
+      <c r="D2" s="8" t="inlineStr"/>
+      <c r="E2" s="8" t="inlineStr"/>
+      <c r="F2" s="8" t="inlineStr"/>
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M2" s="9" t="inlineStr"/>
-      <c r="N2" s="9" t="inlineStr"/>
-      <c r="O2" s="9" t="inlineStr"/>
-      <c r="P2" s="9" t="inlineStr"/>
-      <c r="Q2" s="9" t="inlineStr"/>
-      <c r="R2" s="9" t="inlineStr"/>
-      <c r="S2" s="9" t="inlineStr"/>
-      <c r="T2" s="8" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="8" t="inlineStr"/>
+      <c r="Q2" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="11" t="n"/>
+      <c r="T2" s="8" t="inlineStr"/>
+      <c r="U2" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr"/>
+      <c r="D3" s="8" t="inlineStr"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>MA163
+LEC
+Room: C004
+Dr. Anand</t>
+        </is>
+      </c>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="11" t="n"/>
+      <c r="S3" s="8" t="inlineStr"/>
+      <c r="T3" s="8" t="inlineStr"/>
+      <c r="U3" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr"/>
+      <c r="D4" s="8" t="inlineStr"/>
+      <c r="E4" s="8" t="inlineStr"/>
+      <c r="F4" s="8" t="inlineStr"/>
+      <c r="G4" s="8" t="inlineStr"/>
+      <c r="H4" s="8" t="inlineStr"/>
+      <c r="I4" s="8" t="inlineStr"/>
+      <c r="J4" s="8" t="inlineStr"/>
+      <c r="K4" s="8" t="inlineStr"/>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr"/>
+      <c r="N4" s="8" t="inlineStr"/>
+      <c r="O4" s="8" t="inlineStr"/>
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>MA163
 TUT
-Room: 102
+Room: C004
 Dr. Anand</t>
         </is>
       </c>
-      <c r="U2" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="40" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C3" s="9" t="inlineStr"/>
-      <c r="D3" s="9" t="inlineStr"/>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr"/>
-      <c r="I3" s="9" t="inlineStr"/>
-      <c r="J3" s="9" t="inlineStr"/>
-      <c r="K3" s="9" t="inlineStr"/>
-      <c r="L3" s="10" t="inlineStr">
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M3" s="9" t="inlineStr"/>
-      <c r="N3" s="9" t="inlineStr"/>
-      <c r="O3" s="9" t="inlineStr"/>
-      <c r="P3" s="9" t="inlineStr"/>
-      <c r="Q3" s="9" t="inlineStr"/>
-      <c r="R3" s="9" t="inlineStr"/>
-      <c r="S3" s="9" t="inlineStr"/>
-      <c r="T3" s="9" t="inlineStr"/>
-      <c r="U3" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Wednesday</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr"/>
-      <c r="D4" s="9" t="inlineStr"/>
-      <c r="E4" s="9" t="inlineStr"/>
-      <c r="F4" s="9" t="inlineStr"/>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr"/>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="9" t="inlineStr"/>
-      <c r="K4" s="9" t="inlineStr"/>
-      <c r="L4" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr"/>
-      <c r="N4" s="9" t="inlineStr"/>
-      <c r="O4" s="9" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr"/>
-      <c r="Q4" s="9" t="inlineStr"/>
-      <c r="R4" s="9" t="inlineStr"/>
-      <c r="S4" s="9" t="inlineStr"/>
-      <c r="T4" s="9" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 102
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="H5" s="11" t="n"/>
-      <c r="I5" s="11" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="9" t="inlineStr"/>
-      <c r="L5" s="10" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M5" s="9" t="inlineStr"/>
-      <c r="N5" s="9" t="inlineStr"/>
-      <c r="O5" s="9" t="inlineStr"/>
-      <c r="P5" s="9" t="inlineStr"/>
-      <c r="Q5" s="9" t="inlineStr"/>
-      <c r="R5" s="9" t="inlineStr"/>
-      <c r="S5" s="9" t="inlineStr"/>
-      <c r="T5" s="9" t="inlineStr"/>
+      <c r="M5" s="8" t="inlineStr"/>
+      <c r="N5" s="8" t="inlineStr"/>
+      <c r="O5" s="8" t="inlineStr"/>
+      <c r="P5" s="8" t="inlineStr"/>
+      <c r="Q5" s="8" t="inlineStr"/>
+      <c r="R5" s="8" t="inlineStr"/>
+      <c r="S5" s="8" t="inlineStr"/>
+      <c r="T5" s="8" t="inlineStr"/>
       <c r="U5" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -2297,35 +2307,28 @@
           <t>Minor Slot</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="9" t="inlineStr"/>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr"/>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="9" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr"/>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr"/>
+      <c r="D6" s="8" t="inlineStr"/>
+      <c r="E6" s="8" t="inlineStr"/>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
+      <c r="K6" s="8" t="inlineStr"/>
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>MA163
-LEC
-Room: 102
-Dr. Anand</t>
-        </is>
-      </c>
-      <c r="N6" s="12" t="n"/>
-      <c r="O6" s="9" t="inlineStr"/>
-      <c r="P6" s="9" t="inlineStr"/>
-      <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
-      <c r="S6" s="9" t="inlineStr"/>
-      <c r="T6" s="9" t="inlineStr"/>
+      <c r="M6" s="8" t="inlineStr"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
+      <c r="Q6" s="8" t="inlineStr"/>
+      <c r="R6" s="8" t="inlineStr"/>
+      <c r="S6" s="8" t="inlineStr"/>
+      <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
         <is>
           <t>Minor Slot</t>
@@ -2395,14 +2398,15 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>C004</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="G5:J5"/>
+  <mergeCells count="3">
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2414,7 +2418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2466,13 +2470,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2502,13 +2506,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2522,7 +2526,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -2534,11 +2538,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSE_2_B</t>
+          <t>CSE_2_A</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>4</v>
@@ -2574,13 +2578,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2606,17 +2610,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DSAI_2</t>
+          <t>CSE_2_B</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2630,7 +2634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>LEC</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -2642,17 +2646,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DSAI_2</t>
+          <t>CSE_2_B</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -2678,17 +2682,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ECE_2</t>
+          <t>DSAI_2</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -2697,7 +2701,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>C004</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2714,34 +2718,178 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>DSAI_2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" t="n">
+        <v>16</v>
+      </c>
+      <c r="D9" t="n">
+        <v>18</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>DSAI_2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>ECE_2</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>6</v>
-      </c>
-      <c r="C9" t="n">
-        <v>13</v>
-      </c>
-      <c r="D9" t="n">
-        <v>14</v>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Dr. Anand</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>LEC</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ECE_2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" t="n">
+        <v>18</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>LEC</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>MA163</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ECE_2</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" t="n">
+        <v>11</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Dr. Anand</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>C004</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
         <is>
           <t>MA163</t>
         </is>
